--- a/data/trans_orig/IP16CS1_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP16CS1_2023-Provincia-trans_orig.xlsx
@@ -1447,7 +1447,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>6016</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>88,68%</t>
         </is>
       </c>
     </row>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4352</t>
+          <t>4036</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>59,5%</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2978</t>
+          <t>2526</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3477</t>
+          <t>3523</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,93%</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>863</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1856</t>
+          <t>1701</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2632</t>
+          <t>2154</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2697</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>58,59%</t>
         </is>
       </c>
     </row>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>42,73%</t>
         </is>
       </c>
     </row>
@@ -4175,7 +4175,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>875</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>3298</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2434</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2440</t>
+          <t>2576</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>43,83%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>5237</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>9886</t>
+          <t>10108</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>7878</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>12724</t>
+          <t>12765</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>14888</t>
+          <t>14968</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>21667</t>
+          <t>21648</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,01%</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>3678</t>
+          <t>3756</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>3988</t>
+          <t>4046</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>469</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>5675</t>
+          <t>4932</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>501</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>5770</t>
+          <t>5375</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>21,61%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>2256</t>
+          <t>2576</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>2466</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>384</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>4802</t>
+          <t>4950</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>369</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>5794</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16CS1_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP16CS1_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,64 +720,64 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>471</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>962</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>471</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>471</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>471</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>415</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>415</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>415</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,74 +1402,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2461</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3411</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>72,14%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>19,06%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1220</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2870</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>42,5%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>766</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2503</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>30,62%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2978</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1396</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3914</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>76,1%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>35,66%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>8</t>
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4198</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6016</t>
+          <t>5122</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>86,6%</t>
         </is>
       </c>
     </row>
@@ -1628,74 +1628,74 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1650</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2870</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>57,5%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1737</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2503</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>69,38%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>2</t>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4036</t>
+          <t>4109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>69,46%</t>
         </is>
       </c>
     </row>
@@ -1854,82 +1854,82 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>950</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>936</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2526</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>23,9%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>64,55%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>950</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3523</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>58,3%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>3411</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>3411</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>3411</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>2870</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>2870</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>2870</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>2503</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>2503</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>2503</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>6784</t>
+          <t>5915</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6784</t>
+          <t>5915</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6784</t>
+          <t>5915</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,34 +2089,34 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>314</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>627</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
           <t>1</t>
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>354</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>668</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>981</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2310,82 +2310,82 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>314</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>627</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>762</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>50,0%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>313</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>981</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>397</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>397</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>397</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>354</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>354</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>354</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>981</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>981</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>981</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,74 +2766,74 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1031</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>2562</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>863</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>3744</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>68,42%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>23,05%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>2233</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3380</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>66,05%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>17,78%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>1244</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>7</t>
@@ -2841,27 +2841,27 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3806</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>1423</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4988</t>
+          <t>4411</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>721</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2154</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>19,26%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>57,53%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>766</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2422</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>766</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2922</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>59,74%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>461</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>2088</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>12,32%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>55,77%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>382</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>382</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
@@ -3077,12 +3077,12 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>43,09%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>1031</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>1031</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>1031</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>3744</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>3744</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>3744</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>4988</t>
+          <t>4411</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4988</t>
+          <t>4411</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4988</t>
+          <t>4411</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,12 +3448,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3483,47 +3483,47 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>248</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
@@ -3533,12 +3533,12 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>506</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
@@ -3561,64 +3561,64 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>258</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -3646,12 +3646,12 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>506</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>248</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>248</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>258</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>258</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>258</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>506</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>506</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>506</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4130,72 +4130,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>2442</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>643</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>2849</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>85,72%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>22,56%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>2193</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>2281</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>3220</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>875</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>3684</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>87,41%</t>
-        </is>
-      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,27 +4205,27 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>5413</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5877</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4469,82 +4469,82 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>407</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>464</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>2809</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>12,59%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>76,26%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>407</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
@@ -4554,12 +4554,12 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2576</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>39,51%</t>
         </is>
       </c>
     </row>
@@ -4695,57 +4695,57 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>2849</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>2849</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>2849</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>2193</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>2193</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>2193</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>3684</t>
+          <t>2281</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3684</t>
+          <t>2281</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3684</t>
+          <t>2281</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>5877</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>5877</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>5877</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4812,72 +4812,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>1381</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>60,03%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>9,88%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>1206</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>1050</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>1660</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>2725</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>60,91%</t>
-        </is>
-      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,27 +4887,27 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>2866</t>
+          <t>2431</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>983</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5264,82 +5264,82 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>920</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>2382</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>39,09%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>87,41%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>920</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,99%</t>
         </is>
       </c>
     </row>
@@ -5377,57 +5377,57 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>1206</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>1206</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>1206</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>2725</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>2725</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>2725</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5494,72 +5494,72 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>8670</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>6015</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>10400</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>77,0%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>53,41%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>92,36%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>8048</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>5237</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>10108</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>71,66%</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>46,63%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>90,0%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>10803</t>
+          <t>7099</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>12765</t>
+          <t>9153</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>18851</t>
+          <t>15769</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>14968</t>
+          <t>11843</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>21648</t>
+          <t>18495</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,02%</t>
         </is>
       </c>
     </row>
@@ -5607,72 +5607,72 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>1071</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>3756</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>9,54%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>33,44%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>4046</t>
+          <t>3432</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -5720,72 +5720,72 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>1647</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>14,62%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>2112</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>469</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>4932</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>18,8%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>4,18%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>43,91%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>414</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>5083</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>2493</t>
+          <t>2432</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>675</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>5375</t>
+          <t>6158</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>28,64%</t>
         </is>
       </c>
     </row>
@@ -5833,82 +5833,82 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>407</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>464</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>2576</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>3,4%</t>
-        </is>
-      </c>
-      <c r="O49" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P49" s="2" t="inlineStr">
-        <is>
-          <t>18,87%</t>
-        </is>
-      </c>
-      <c r="Q49" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>407</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>2466</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -5946,107 +5946,107 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>318</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4658</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>4950</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>14,66%</t>
-        </is>
-      </c>
-      <c r="O50" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>36,26%</t>
-        </is>
-      </c>
-      <c r="Q50" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>311</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>5794</t>
+          <t>5013</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,32%</t>
         </is>
       </c>
     </row>
@@ -6059,57 +6059,57 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11260</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>11260</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>11260</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>11231</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>11231</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>11231</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>13649</t>
+          <t>10241</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>13649</t>
+          <t>10241</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>13649</t>
+          <t>10241</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>24880</t>
+          <t>21501</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>24880</t>
+          <t>21501</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>24880</t>
+          <t>21501</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
